--- a/src/attributions/attributions_ig_traj_299.xlsx
+++ b/src/attributions/attributions_ig_traj_299.xlsx
@@ -1568,34 +1568,34 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.06056250654695616</v>
+        <v>-0.02786892888161591</v>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>-0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.04986279297136532</v>
+        <v>0.01359963610322018</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0002940285466769232</v>
+        <v>-0.01975511284127759</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004369799158650303</v>
+        <v>-0.003253280626950881</v>
       </c>
       <c r="K3" t="n">
         <v>-0</v>
@@ -1607,40 +1607,40 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0.00473615013664495</v>
+        <v>0.0006220044222239862</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0004592490475446961</v>
+        <v>0.002302617079280415</v>
       </c>
       <c r="Q3" t="n">
         <v>-0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.07236008768041637</v>
+        <v>0.02246715487532366</v>
       </c>
       <c r="T3" t="n">
         <v>-0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.09310899386183623</v>
+        <v>0.01943618395986903</v>
       </c>
       <c r="X3" t="n">
         <v>-0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-7.136624076521154e-05</v>
+        <v>-0.01537357155350929</v>
       </c>
       <c r="Z3" t="n">
         <v>-0</v>
@@ -1649,7 +1649,7 @@
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.03874234097672831</v>
+        <v>0.003427457791646328</v>
       </c>
       <c r="AC3" t="n">
         <v>-0</v>
@@ -1658,25 +1658,25 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.1376605241449312</v>
+        <v>-0.02540764355537866</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.01158778106857453</v>
+        <v>-0.02399778771064515</v>
       </c>
       <c r="AI3" t="n">
         <v>-0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.01380307235340537</v>
+        <v>0.00847547286456485</v>
       </c>
       <c r="AL3" t="n">
         <v>-0</v>
@@ -1685,82 +1685,82 @@
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.01796920497142673</v>
+        <v>0.0383175297468698</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.01348800883414838</v>
+        <v>-0.00632481328110616</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS3" t="n">
         <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.1189884605780483</v>
+        <v>-0.02091698933210228</v>
       </c>
       <c r="AU3" t="n">
         <v>-0</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.1675673837677019</v>
+        <v>0.04482217892452542</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.01104118604474351</v>
+        <v>-0.01876096915911531</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.06678979236445506</v>
+        <v>-0.01508991213545338</v>
       </c>
       <c r="BD3" t="n">
         <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.05226757060849158</v>
+        <v>-0.02004253941547107</v>
       </c>
       <c r="BH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>-0.006257332448361527</v>
+        <v>-0.009274973126340503</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>-0.002754958383625068</v>
+        <v>0.03862102704827943</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BN3" t="n">
         <v>-0</v>
@@ -1769,13 +1769,13 @@
         <v>-0</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.006729876636726047</v>
+        <v>0.02334300989672726</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.03106076589740729</v>
+        <v>-0.0009192060227398807</v>
       </c>
       <c r="BS3" t="n">
         <v>-0</v>
@@ -1784,10 +1784,10 @@
         <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.03246438288360552</v>
+        <v>-0.005215905495389824</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BW3" t="n">
         <v>-0</v>
@@ -1796,40 +1796,40 @@
         <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.03410284726280625</v>
+        <v>0.02913188507934325</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA3" t="n">
-        <v>-0.000860381306517546</v>
+        <v>-0.01033508528605515</v>
       </c>
       <c r="CB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC3" t="n">
         <v>0</v>
       </c>
       <c r="CD3" t="n">
-        <v>-0.04595209418595242</v>
+        <v>0.01982772817955737</v>
       </c>
       <c r="CE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG3" t="n">
         <v>0</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.01088439927003507</v>
+        <v>-0.02259632715285675</v>
       </c>
       <c r="CI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.004902424866768</v>
+        <v>0.01129406625521932</v>
       </c>
       <c r="CK3" t="n">
         <v>-0</v>
@@ -1838,25 +1838,25 @@
         <v>-0</v>
       </c>
       <c r="CM3" t="n">
-        <v>-0.036783164129375</v>
+        <v>-0.001545857532429557</v>
       </c>
       <c r="CN3" t="n">
         <v>0</v>
       </c>
       <c r="CO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP3" t="n">
         <v>-0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.02321161875610248</v>
+        <v>-0.03722072428940856</v>
       </c>
       <c r="CR3" t="n">
         <v>-0</v>
       </c>
       <c r="CS3" t="n">
-        <v>-0.005383512830085293</v>
+        <v>0.009359625734575995</v>
       </c>
       <c r="CT3" t="n">
         <v>-0</v>
@@ -1865,25 +1865,25 @@
         <v>-0</v>
       </c>
       <c r="CV3" t="n">
-        <v>-0.02901898558690898</v>
+        <v>0.01583966730389294</v>
       </c>
       <c r="CW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CX3" t="n">
         <v>-0</v>
       </c>
       <c r="CY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.01476379753258272</v>
+        <v>-0.02950110405627189</v>
       </c>
       <c r="DA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.004824678625912762</v>
+        <v>0.01549452709509967</v>
       </c>
       <c r="DC3" t="n">
         <v>0</v>
@@ -1892,7 +1892,7 @@
         <v>0</v>
       </c>
       <c r="DE3" t="n">
-        <v>-0.01176681242251756</v>
+        <v>0.002539817689956104</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -1904,13 +1904,13 @@
         <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.008661361889558567</v>
+        <v>-0.02424979523621847</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK3" t="n">
-        <v>-0.01024083915435542</v>
+        <v>0.003254440497553733</v>
       </c>
       <c r="DL3" t="n">
         <v>-0</v>
@@ -1919,7 +1919,7 @@
         <v>-0</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.006501131222391553</v>
+        <v>-0.006309932091480267</v>
       </c>
       <c r="DO3" t="n">
         <v>0</v>
@@ -1928,25 +1928,25 @@
         <v>-0</v>
       </c>
       <c r="DQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>-0.05186894350328648</v>
+        <v>-0.0229288541966815</v>
       </c>
       <c r="DS3" t="n">
         <v>-0</v>
       </c>
       <c r="DT3" t="n">
-        <v>-0.00964744040007557</v>
+        <v>0.006840083020336979</v>
       </c>
       <c r="DU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.01127384063077184</v>
+        <v>0.004047241039780452</v>
       </c>
       <c r="DX3" t="n">
         <v>0</v>
@@ -1958,13 +1958,13 @@
         <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.02740283134883308</v>
+        <v>-0.002996759118027361</v>
       </c>
       <c r="EB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC3" t="n">
-        <v>-0.0008285955571601142</v>
+        <v>0.03156482997741717</v>
       </c>
       <c r="ED3" t="n">
         <v>0</v>
@@ -1973,34 +1973,34 @@
         <v>-0</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0.04555556302131265</v>
+        <v>0.02458193801330648</v>
       </c>
       <c r="EG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH3" t="n">
         <v>-0</v>
       </c>
       <c r="EI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.02005347990337207</v>
+        <v>-0.02165803869698094</v>
       </c>
       <c r="EK3" t="n">
         <v>0</v>
       </c>
       <c r="EL3" t="n">
-        <v>0.006991384621589579</v>
+        <v>0.006833474302629623</v>
       </c>
       <c r="EM3" t="n">
         <v>-0</v>
       </c>
       <c r="EN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO3" t="n">
-        <v>-0.01773494646185129</v>
+        <v>0.01744508096030569</v>
       </c>
       <c r="EP3" t="n">
         <v>0</v>
@@ -2009,25 +2009,25 @@
         <v>0</v>
       </c>
       <c r="ER3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.08449104595847517</v>
+        <v>-0.02832743050499036</v>
       </c>
       <c r="ET3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU3" t="n">
-        <v>-0.001216557915076114</v>
+        <v>-0.001804092235268539</v>
       </c>
       <c r="EV3" t="n">
         <v>-0</v>
       </c>
       <c r="EW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX3" t="n">
-        <v>-0.02435634025120847</v>
+        <v>0.02148469173838996</v>
       </c>
       <c r="EY3" t="n">
         <v>0</v>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="FA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.009265443573620398</v>
+        <v>-0.03395582919650161</v>
       </c>
       <c r="FC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD3" t="n">
-        <v>-0.0003035723023645657</v>
+        <v>0.01743249239712981</v>
       </c>
       <c r="FE3" t="n">
         <v>-0</v>
@@ -2054,25 +2054,25 @@
         <v>-0</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.0237505160957097</v>
+        <v>0.03088223254752343</v>
       </c>
       <c r="FH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FI3" t="n">
         <v>-0</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.02729071330649734</v>
+        <v>-0.01434697050801695</v>
       </c>
       <c r="FL3" t="n">
         <v>-0</v>
       </c>
       <c r="FM3" t="n">
-        <v>0.01284457554654648</v>
+        <v>-0.002898624875092574</v>
       </c>
       <c r="FN3" t="n">
         <v>-0</v>
@@ -2081,25 +2081,25 @@
         <v>0</v>
       </c>
       <c r="FP3" t="n">
-        <v>-0.05883331799219409</v>
+        <v>0.00130425495579766</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS3" t="n">
         <v>-0</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.09757758498970509</v>
+        <v>-0.01957187960035212</v>
       </c>
       <c r="FU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV3" t="n">
-        <v>0.03564156558916652</v>
+        <v>0.01320017332159824</v>
       </c>
       <c r="FW3" t="n">
         <v>-0</v>
@@ -2108,7 +2108,7 @@
         <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>-0.02831286479977418</v>
+        <v>0.01421535624087011</v>
       </c>
       <c r="FZ3" t="n">
         <v>0</v>
@@ -2120,19 +2120,19 @@
         <v>-0</v>
       </c>
       <c r="GC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE3" t="n">
-        <v>-0.05022748790130408</v>
+        <v>0.01643847674151674</v>
       </c>
       <c r="GF3" t="n">
         <v>0</v>
       </c>
       <c r="GG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2140,19 +2140,19 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.2170461487869008</v>
+        <v>0.3090452411823946</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.05975528358099093</v>
+        <v>0.06858197226475905</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2201138667216569</v>
+        <v>-0.2580937766420587</v>
       </c>
       <c r="G4" t="n">
         <v>-0</v>
@@ -2161,55 +2161,55 @@
         <v>-0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.04624854970930557</v>
+        <v>0.09468232161605115</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.003803729843468771</v>
+        <v>-0.004537381423014021</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0054426775770867</v>
+        <v>0.005321822482219983</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>-0</v>
       </c>
       <c r="R4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0121931202114987</v>
+        <v>-0.1056316874383861</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.0868252484346145</v>
+        <v>-0.08876752135260182</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.03073929221168106</v>
+        <v>-0.1179686885115422</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z4" t="n">
         <v>-0</v>
@@ -2218,22 +2218,22 @@
         <v>-0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.0382599538654256</v>
+        <v>0.1204909075576635</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.1248757428227917</v>
+        <v>0.05574707491768357</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.05272487440239207</v>
+        <v>0.1426421313689668</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
@@ -2242,40 +2242,40 @@
         <v>-0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.04727546788309357</v>
+        <v>0.1240628564336683</v>
       </c>
       <c r="AM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.04069551459811029</v>
+        <v>-0.05468214925075224</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.1266174540529857</v>
+        <v>-0.2334080160793761</v>
       </c>
       <c r="AQ4" t="n">
         <v>-0</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS4" t="n">
         <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.2648216490784184</v>
+        <v>0.6605533326792286</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
@@ -2284,25 +2284,25 @@
         <v>-0</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.158183454195903</v>
+        <v>-0.2446433548197511</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.4032229626462012</v>
+        <v>-0.4145454973390755</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA4" t="n">
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.1258434913437113</v>
+        <v>0.1155903603534005</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
@@ -2311,13 +2311,13 @@
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.0321798712052718</v>
+        <v>0.06354345695446442</v>
       </c>
       <c r="BH4" t="n">
-        <v>-0.07420996449020013</v>
+        <v>-0.1682280474042692</v>
       </c>
       <c r="BI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
         <v>-0</v>
@@ -2329,73 +2329,73 @@
         <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>-0.001813804961735719</v>
+        <v>0.07024336343322565</v>
       </c>
       <c r="BN4" t="n">
         <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP4" t="n">
-        <v>-0.02494621923470392</v>
+        <v>0.08542670307367577</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.02298061902257294</v>
+        <v>0.1569639767492343</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.07039851144054037</v>
+        <v>0.2210686711751446</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.1132601381946213</v>
+        <v>-0.1019873709470566</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0.1328434026368685</v>
+        <v>-0.2767261156106648</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB4" t="n">
         <v>-0</v>
       </c>
       <c r="CC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD4" t="n">
         <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.1073822586619718</v>
+        <v>-0.2579791212192447</v>
       </c>
       <c r="CF4" t="n">
         <v>0</v>
       </c>
       <c r="CG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.03080327952085105</v>
+        <v>-0.06246542476836745</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.1152601678946842</v>
+        <v>0.1771601283681623</v>
       </c>
       <c r="CJ4" t="n">
         <v>0</v>
@@ -2404,58 +2404,58 @@
         <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
         <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.004952620690293392</v>
+        <v>-0.2419717810089807</v>
       </c>
       <c r="CO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP4" t="n">
         <v>-0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.04683927353884149</v>
+        <v>0.05823623442732907</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.01088647837865527</v>
+        <v>0.1487782641373321</v>
       </c>
       <c r="CS4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.08796629451604106</v>
+        <v>-0.2459956557600103</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
         <v>0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.01803138483404039</v>
+        <v>-0.05932614306533676</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.1334773349378525</v>
+        <v>0.1517059269718812</v>
       </c>
       <c r="DB4" t="n">
         <v>-0</v>
       </c>
       <c r="DC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD4" t="n">
         <v>0</v>
@@ -2464,73 +2464,73 @@
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.05390966898013396</v>
+        <v>-0.1304530710247239</v>
       </c>
       <c r="DG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.03964686353397251</v>
+        <v>-0.05258112797751905</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.004301978598605613</v>
+        <v>0.1386717639002207</v>
       </c>
       <c r="DK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL4" t="n">
         <v>0</v>
       </c>
       <c r="DM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.01465169216944954</v>
+        <v>-0.09144986067297706</v>
       </c>
       <c r="DP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.1168675655337137</v>
+        <v>0.001259247068048539</v>
       </c>
       <c r="DS4" t="n">
-        <v>-0.01375070556506886</v>
+        <v>0.07686626210868473</v>
       </c>
       <c r="DT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.05133033603566994</v>
+        <v>0.1531542436854383</v>
       </c>
       <c r="DY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ4" t="n">
         <v>0</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.01138238411469794</v>
+        <v>-0.04031904439138505</v>
       </c>
       <c r="EB4" t="n">
-        <v>-0.01486296360789663</v>
+        <v>0.1717622430373899</v>
       </c>
       <c r="EC4" t="n">
         <v>-0</v>
@@ -2542,25 +2542,25 @@
         <v>-0</v>
       </c>
       <c r="EF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.1183834044830427</v>
+        <v>-0.1246728294020258</v>
       </c>
       <c r="EH4" t="n">
         <v>0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>-0.00657862766244103</v>
+        <v>-0.0876946304949535</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.124754724094843</v>
+        <v>0.15251226559154</v>
       </c>
       <c r="EL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM4" t="n">
         <v>-0</v>
@@ -2569,10 +2569,10 @@
         <v>-0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.04773220213343761</v>
+        <v>-0.1638853005417523</v>
       </c>
       <c r="EQ4" t="n">
         <v>-0</v>
@@ -2581,37 +2581,37 @@
         <v>0</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.03458485190971846</v>
+        <v>-0.1924983131969843</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.05692480113302847</v>
+        <v>0.1655584447708482</v>
       </c>
       <c r="EU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW4" t="n">
         <v>-0</v>
       </c>
       <c r="EX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.08614608822317865</v>
+        <v>-0.2373045676457447</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.03335915137871331</v>
+        <v>-0.1187707585295715</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.1202570701488062</v>
+        <v>0.1607772201807394</v>
       </c>
       <c r="FD4" t="n">
         <v>0</v>
@@ -2623,85 +2623,85 @@
         <v>-0</v>
       </c>
       <c r="FG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.07584601399976601</v>
+        <v>-0.1282552618633541</v>
       </c>
       <c r="FI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ4" t="n">
         <v>-0</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.06607827494170669</v>
+        <v>-0.06166041973372087</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.1369253727303383</v>
+        <v>0.2840597021542615</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
       </c>
       <c r="FN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO4" t="n">
         <v>0</v>
       </c>
       <c r="FP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-0.1581160502589445</v>
+        <v>-0.01354226086905758</v>
       </c>
       <c r="FR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS4" t="n">
         <v>-0</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.05833573986616377</v>
+        <v>0.06358466761025044</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.08684198627359421</v>
+        <v>0.04977563576019872</v>
       </c>
       <c r="FV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.04502832762619102</v>
+        <v>-0.1201723210806603</v>
       </c>
       <c r="GA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB4" t="n">
         <v>0</v>
       </c>
       <c r="GC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0.02892805697973632</v>
+        <v>0.1844128726722734</v>
       </c>
       <c r="GE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="5">
@@ -3278,7 +3278,7 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.06188241556675032</v>
+        <v>0.356990222936502</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -3287,25 +3287,25 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.00919528496563511</v>
+        <v>0.0220525717311173</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.02096794634652264</v>
+        <v>-0.139113602231268</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01583180676886485</v>
+        <v>0.1384412850576173</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -3314,40 +3314,40 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.003870392348116805</v>
+        <v>-0.02962947320802266</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.01137817643241358</v>
+        <v>-0.08891539115063261</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.00221558817205783</v>
+        <v>0.1285754117412413</v>
       </c>
       <c r="U6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.004864649138517006</v>
+        <v>-0.1260306164882175</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001368053858590308</v>
+        <v>-0.03274342816722655</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z6" t="n">
         <v>-0</v>
@@ -3359,79 +3359,79 @@
         <v>-0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.0109584462755314</v>
+        <v>0.0282460201890781</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.0228047992025442</v>
+        <v>-0.2331253679905819</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.0007665886333811035</v>
+        <v>0.03407016642560937</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ6" t="n">
         <v>-0</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.004387812711740875</v>
+        <v>0.1902961099298199</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.01112489320974974</v>
+        <v>0.1350259023472225</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.01606030600129673</v>
+        <v>-0.1387497303333746</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR6" t="n">
         <v>-0</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.08283945622608539</v>
+        <v>0.7401460792974859</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.004261689772855511</v>
+        <v>-0.212844233455272</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.005681785358982464</v>
+        <v>-0.182845444988128</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB6" t="n">
         <v>0</v>
@@ -3440,7 +3440,7 @@
         <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.02782589872503623</v>
+        <v>-0.02603101642158416</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
@@ -3449,40 +3449,40 @@
         <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.019549124877929</v>
+        <v>-0.06256612241091052</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.04848099779482846</v>
+        <v>-0.1058755028573734</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
         <v>-0</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.02899641128218291</v>
+        <v>0.04287204020722209</v>
       </c>
       <c r="BN6" t="n">
         <v>-0</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.02612550003476191</v>
+        <v>0.130246068827055</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.004639947585217081</v>
+        <v>0.1469991435735549</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS6" t="n">
         <v>-0</v>
@@ -3494,7 +3494,7 @@
         <v>-0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.02863953808049267</v>
+        <v>0.371863239996362</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
@@ -3503,43 +3503,43 @@
         <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.005118974974840005</v>
+        <v>-0.03343428744894922</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.004552350786474342</v>
+        <v>-0.2357657079612692</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB6" t="n">
         <v>-0</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.01841412203212578</v>
+        <v>-0.2366367439352777</v>
       </c>
       <c r="CF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG6" t="n">
         <v>0</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.002118904109182733</v>
+        <v>-0.02475558903598251</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.01906843224728092</v>
+        <v>0.1593026504163285</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL6" t="n">
         <v>0</v>
@@ -3548,49 +3548,49 @@
         <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.00527981981179559</v>
+        <v>-0.1583482802732657</v>
       </c>
       <c r="CO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP6" t="n">
         <v>-0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.004108655922119841</v>
+        <v>0.08265434223804126</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.0007809106633622541</v>
+        <v>-0.0005368565063359071</v>
       </c>
       <c r="CS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT6" t="n">
         <v>0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.01412110748908113</v>
+        <v>-0.2141646274406068</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.003638293946648316</v>
+        <v>-0.02103884702721226</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.01873158737210883</v>
+        <v>0.1592680513527125</v>
       </c>
       <c r="DB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC6" t="n">
         <v>0</v>
@@ -3602,52 +3602,52 @@
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.004318032461428666</v>
+        <v>-0.03500064536337061</v>
       </c>
       <c r="DG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH6" t="n">
         <v>-0</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.01812079702664662</v>
+        <v>-0.07243342027773597</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.003546490182692985</v>
+        <v>0.0381981839502944</v>
       </c>
       <c r="DK6" t="n">
         <v>0</v>
       </c>
       <c r="DL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.005923831458935125</v>
+        <v>-0.1004499681973499</v>
       </c>
       <c r="DP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ6" t="n">
         <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>-8.95803137745175e-05</v>
+        <v>0.005045798389804882</v>
       </c>
       <c r="DS6" t="n">
-        <v>-0.006199084901461501</v>
+        <v>0.01096105966138417</v>
       </c>
       <c r="DT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV6" t="n">
         <v>-0</v>
@@ -3656,46 +3656,46 @@
         <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.01775048927623112</v>
+        <v>0.08336716842357894</v>
       </c>
       <c r="DY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.03205357836121387</v>
+        <v>-0.07633904146178534</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.0005930411331872502</v>
+        <v>0.1252512036742044</v>
       </c>
       <c r="EC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.01384135386648185</v>
+        <v>-0.04290063506293436</v>
       </c>
       <c r="EH6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI6" t="n">
         <v>0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>-0.001024316817494005</v>
+        <v>-0.1298588274190507</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.01136739744581012</v>
+        <v>0.08025539296084284</v>
       </c>
       <c r="EL6" t="n">
         <v>-0</v>
@@ -3707,10 +3707,10 @@
         <v>0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.0151176610700421</v>
+        <v>-0.120314527228706</v>
       </c>
       <c r="EQ6" t="n">
         <v>-0</v>
@@ -3719,37 +3719,37 @@
         <v>0</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.008658470596225855</v>
+        <v>-0.1981833145509987</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.004997676992950147</v>
+        <v>0.04087401940103448</v>
       </c>
       <c r="EU6" t="n">
         <v>0</v>
       </c>
       <c r="EV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW6" t="n">
         <v>0</v>
       </c>
       <c r="EX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.01643971944646957</v>
+        <v>-0.2354908320712711</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA6" t="n">
         <v>0</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.004044660982815073</v>
+        <v>-0.06249427331599514</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.02020196961973531</v>
+        <v>0.1370694691002747</v>
       </c>
       <c r="FD6" t="n">
         <v>0</v>
@@ -3758,13 +3758,13 @@
         <v>-0</v>
       </c>
       <c r="FF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.0001931502163546776</v>
+        <v>-0.2129666420269714</v>
       </c>
       <c r="FI6" t="n">
         <v>0</v>
@@ -3773,70 +3773,70 @@
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.02621339499649919</v>
+        <v>0.07817244621478675</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.01979613233959642</v>
+        <v>0.224937528140058</v>
       </c>
       <c r="FM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO6" t="n">
         <v>0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.001545785384382836</v>
+        <v>-0.02923275999523168</v>
       </c>
       <c r="FR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS6" t="n">
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.0004305234250826192</v>
+        <v>-0.0009684823460585909</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.008614041637559848</v>
+        <v>0.0984252938980041</v>
       </c>
       <c r="FV6" t="n">
         <v>-0</v>
       </c>
       <c r="FW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.02722373650709928</v>
+        <v>-0.08883527549646714</v>
       </c>
       <c r="GA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB6" t="n">
         <v>-0</v>
       </c>
       <c r="GC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.006754551429212806</v>
+        <v>0.1032511967407685</v>
       </c>
       <c r="GE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG6" t="n">
         <v>0</v>
@@ -3847,22 +3847,22 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1219184922435678</v>
+        <v>0.3596587934806102</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.00341922424569569</v>
+        <v>0.04701253394394463</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.07554215579938897</v>
+        <v>-0.1737893151797207</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H7" t="n">
         <v>-0</v>
@@ -3874,7 +3874,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.04787212156262561</v>
+        <v>0.1972385839958785</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -3883,64 +3883,64 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.001065919297129571</v>
+        <v>-0.02050356167385696</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.04436512974791736</v>
+        <v>-0.1048566585218731</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.005346369061070973</v>
+        <v>0.1008062043297155</v>
       </c>
       <c r="U7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.01565563709737232</v>
+        <v>-0.1309635511870953</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.001837912597843148</v>
+        <v>-0.01664052696451674</v>
       </c>
       <c r="Y7" t="n">
         <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.0198400566526704</v>
+        <v>0.04464816045266069</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.02141697196959443</v>
+        <v>-0.2257415515704195</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.003131864756851275</v>
+        <v>-0.08593729336544681</v>
       </c>
       <c r="AH7" t="n">
         <v>0</v>
@@ -3955,22 +3955,22 @@
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.02090540267192832</v>
+        <v>0.1649419863892808</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.005648328108760059</v>
+        <v>0.1102783684175098</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0.03744228037387603</v>
+        <v>-0.1054153519546961</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR7" t="n">
         <v>-0</v>
@@ -3979,22 +3979,22 @@
         <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.1430254650529754</v>
+        <v>0.6314944983237311</v>
       </c>
       <c r="AV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW7" t="n">
         <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.001972021399295735</v>
+        <v>-0.1430461270688154</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0.0804899250187244</v>
+        <v>-0.1939985228435721</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
@@ -4009,7 +4009,7 @@
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.05045559657957903</v>
+        <v>-0.00166960569581843</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
@@ -4018,10 +4018,10 @@
         <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.03946647271976187</v>
+        <v>-0.05358596249987858</v>
       </c>
       <c r="BH7" t="n">
-        <v>-0.07253849888305285</v>
+        <v>-0.1598287888623418</v>
       </c>
       <c r="BI7" t="n">
         <v>-0</v>
@@ -4030,28 +4030,28 @@
         <v>-0</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.03371498684132956</v>
+        <v>0.03597891687574522</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.01956870652075751</v>
+        <v>0.07254997340886034</v>
       </c>
       <c r="BQ7" t="n">
-        <v>-0.003965689451432413</v>
+        <v>0.04722070850917186</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
         <v>0</v>
@@ -4060,10 +4060,10 @@
         <v>0</v>
       </c>
       <c r="BU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.05116806930114831</v>
+        <v>0.308161113444726</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
@@ -4072,13 +4072,13 @@
         <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.001303406701031689</v>
+        <v>-0.02883878609189162</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0.02388984077286906</v>
+        <v>-0.1354880624237273</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB7" t="n">
         <v>-0</v>
@@ -4090,22 +4090,22 @@
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.03740482327755392</v>
+        <v>-0.217174321146221</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.006396417242737202</v>
+        <v>-0.04840076487036296</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.03789734780422618</v>
+        <v>0.1321887507124207</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
         <v>0</v>
@@ -4117,49 +4117,49 @@
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.006160283191042309</v>
+        <v>-0.1295911565612802</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.0132598649037093</v>
+        <v>0.05421167611691716</v>
       </c>
       <c r="CR7" t="n">
-        <v>-0.002855032719408294</v>
+        <v>0.009374606953762575</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
       </c>
       <c r="CT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV7" t="n">
         <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.03239953157570981</v>
+        <v>-0.1940197640021956</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
         <v>0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.0004151191401548538</v>
+        <v>-0.04769959422431577</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.04071832288578545</v>
+        <v>0.1356734250807938</v>
       </c>
       <c r="DB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC7" t="n">
         <v>-0</v>
@@ -4171,19 +4171,19 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.009980225018701914</v>
+        <v>-0.05911762011671604</v>
       </c>
       <c r="DG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.007550856845062566</v>
+        <v>-0.05057888358632381</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.001557597627415997</v>
+        <v>0.03674997328495205</v>
       </c>
       <c r="DK7" t="n">
         <v>0</v>
@@ -4195,28 +4195,28 @@
         <v>0</v>
       </c>
       <c r="DN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.00469659320587397</v>
+        <v>-0.1073022857837814</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.003814337520042726</v>
+        <v>-0.001245428164752054</v>
       </c>
       <c r="DS7" t="n">
-        <v>-0.01283373467887755</v>
+        <v>0.08686405340242774</v>
       </c>
       <c r="DT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV7" t="n">
         <v>-0</v>
@@ -4225,19 +4225,19 @@
         <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.02192092560421685</v>
+        <v>0.02309928583987801</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.03172828514516485</v>
+        <v>0.1047281624243083</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.003640348428581356</v>
+        <v>0.1229969291436613</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
@@ -4246,28 +4246,28 @@
         <v>-0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF7" t="n">
         <v>-0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.0329163327992961</v>
+        <v>-0.05047978054719228</v>
       </c>
       <c r="EH7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI7" t="n">
         <v>0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.002021538045435149</v>
+        <v>-0.1002014461203396</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.02793303738141083</v>
+        <v>0.04271529679866341</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
         <v>-0</v>
@@ -4276,64 +4276,64 @@
         <v>0</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.0322274775026795</v>
+        <v>-0.1020339593147921</v>
       </c>
       <c r="EQ7" t="n">
         <v>-0</v>
       </c>
       <c r="ER7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.007628490835113849</v>
+        <v>-0.1000891848899627</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.02848116422246836</v>
+        <v>0.08794312527388219</v>
       </c>
       <c r="EU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX7" t="n">
         <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.03338839772884131</v>
+        <v>-0.2149313210351812</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA7" t="n">
         <v>-0</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.001829895696801994</v>
+        <v>-0.07378981977737391</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.03673689978036491</v>
+        <v>0.1200942846639016</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
         <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.008528316195541794</v>
+        <v>-0.2422941632775134</v>
       </c>
       <c r="FI7" t="n">
         <v>0</v>
@@ -4342,70 +4342,70 @@
         <v>-0</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.02280911646014498</v>
+        <v>0.06524182636341437</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.0214696168193547</v>
+        <v>0.2489491057001093</v>
       </c>
       <c r="FM7" t="n">
         <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO7" t="n">
         <v>0</v>
       </c>
       <c r="FP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.007765853870291177</v>
+        <v>-0.03214507368865865</v>
       </c>
       <c r="FR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS7" t="n">
         <v>-0</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.001764752710660483</v>
+        <v>-0.008439801244018977</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.02597642590847323</v>
+        <v>0.1364030772445146</v>
       </c>
       <c r="FV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.02232209276413775</v>
+        <v>-0.05369989581638961</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.006911032116960865</v>
+        <v>0.009347113875979477</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG7" t="n">
         <v>0</v>
@@ -4985,154 +4985,154 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2197667908849288</v>
+        <v>0.5578233739821539</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.06763846107580557</v>
+        <v>-0.002276327687486007</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.04778675991960982</v>
+        <v>0.06526552827665759</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.06871271768981697</v>
+        <v>-0.2160888884973607</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1277587378901571</v>
+        <v>0.4993542099199259</v>
       </c>
       <c r="L9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.05462433734185475</v>
+        <v>-0.1120233051405439</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.02946027265860778</v>
+        <v>-0.04205129660193223</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.04317462987899704</v>
+        <v>-0.1126920379458048</v>
       </c>
       <c r="P9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.04937144377824131</v>
+        <v>0.1385991341198753</v>
       </c>
       <c r="U9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.01514882904960532</v>
+        <v>-0.1466654076126097</v>
       </c>
       <c r="W9" t="n">
-        <v>0.02754256094888084</v>
+        <v>-0.1434895456064261</v>
       </c>
       <c r="X9" t="n">
-        <v>0.02309280354320864</v>
+        <v>0.006694252528539393</v>
       </c>
       <c r="Y9" t="n">
         <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.01840914406672245</v>
+        <v>0.1465613418905699</v>
       </c>
       <c r="AD9" t="n">
         <v>-0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.04367134585154401</v>
+        <v>-0.3394198412530866</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.00125026988709313</v>
+        <v>-0.2172587604576743</v>
       </c>
       <c r="AG9" t="n">
-        <v>-0.0119005617031316</v>
+        <v>-0.1541780242071397</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.001656097944060184</v>
+        <v>0.2670730249954267</v>
       </c>
       <c r="AM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.03113131002247291</v>
+        <v>-0.1450366566588353</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.01359647667537389</v>
+        <v>0.1670010875248334</v>
       </c>
       <c r="AP9" t="n">
-        <v>-0.02883069633471027</v>
+        <v>-0.1910001426642614</v>
       </c>
       <c r="AQ9" t="n">
         <v>-0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS9" t="n">
         <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.3244104642102168</v>
+        <v>0.8155728531843117</v>
       </c>
       <c r="AV9" t="n">
         <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0.009397941958847021</v>
+        <v>-0.004228945384757997</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.04677756664568994</v>
+        <v>-0.1414491872986918</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.04363053488610782</v>
+        <v>-0.1224664155625487</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
@@ -5141,58 +5141,58 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
         <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.02025646108011033</v>
+        <v>0.01816792888228675</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.04292178833260405</v>
+        <v>-0.0916837570388969</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.09432179855542493</v>
+        <v>-0.1375731519483069</v>
       </c>
       <c r="BH9" t="n">
-        <v>-0.1236468880906035</v>
+        <v>-0.2544931411963827</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL9" t="n">
         <v>-0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.07009425816355222</v>
+        <v>0.03899142412124584</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.04521396862708939</v>
+        <v>-0.002509924346538094</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.06597463524192362</v>
+        <v>0.1470223782879805</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.01369774018282329</v>
+        <v>0.009761877696496859</v>
       </c>
       <c r="BR9" t="n">
         <v>0</v>
       </c>
       <c r="BS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT9" t="n">
         <v>0</v>
@@ -5201,19 +5201,19 @@
         <v>0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.1198428804506877</v>
+        <v>0.3776346301940939</v>
       </c>
       <c r="BW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.02495097964529424</v>
+        <v>-0.086450497649896</v>
       </c>
       <c r="BY9" t="n">
-        <v>-0.01273602252141491</v>
+        <v>-0.009874549155010388</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.02348861010011724</v>
+        <v>-0.1655355969374503</v>
       </c>
       <c r="CA9" t="n">
         <v>-0</v>
@@ -5222,28 +5222,28 @@
         <v>-0</v>
       </c>
       <c r="CC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.05866956524858317</v>
+        <v>-0.2702416595451853</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.006510601720493901</v>
+        <v>0.04023978871117893</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.001319947976155638</v>
+        <v>-0.06583626314199072</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.04405373934626156</v>
+        <v>0.1165501145961387</v>
       </c>
       <c r="CJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK9" t="n">
         <v>0</v>
@@ -5252,301 +5252,301 @@
         <v>0</v>
       </c>
       <c r="CM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.02195677800762075</v>
+        <v>-0.1933365221164951</v>
       </c>
       <c r="CO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.03441075806007817</v>
+        <v>0.139470317511012</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.01931733497489368</v>
+        <v>0.01906795409302841</v>
       </c>
       <c r="CR9" t="n">
-        <v>-0.0164019664527915</v>
+        <v>0.08857434423209844</v>
       </c>
       <c r="CS9" t="n">
         <v>0</v>
       </c>
       <c r="CT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.05104901735226843</v>
+        <v>-0.2450263319433091</v>
       </c>
       <c r="CX9" t="n">
         <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.02359816977854992</v>
+        <v>0.04563486735221417</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.004730084119904106</v>
+        <v>-0.08257239161756685</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.05180191264958028</v>
+        <v>0.1122135875887873</v>
       </c>
       <c r="DB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD9" t="n">
         <v>0</v>
       </c>
       <c r="DE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.01321611014989833</v>
+        <v>-0.048787806640476</v>
       </c>
       <c r="DG9" t="n">
         <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.07826675187084432</v>
+        <v>-0.02973966325784675</v>
       </c>
       <c r="DI9" t="n">
-        <v>-0.01561664936553353</v>
+        <v>0.4731048605914669</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.003009584250383389</v>
+        <v>0.02178720578549196</v>
       </c>
       <c r="DK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL9" t="n">
         <v>0</v>
       </c>
       <c r="DM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN9" t="n">
         <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.03798320532819007</v>
+        <v>-0.09494536045495842</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.02724777894867367</v>
+        <v>0.06337540368320493</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.0227020118237608</v>
+        <v>-0.09776319057018079</v>
       </c>
       <c r="DS9" t="n">
-        <v>-0.02653254520503731</v>
+        <v>0.1543843604885614</v>
       </c>
       <c r="DT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW9" t="n">
         <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.006054731141806383</v>
+        <v>0.1476123856479851</v>
       </c>
       <c r="DY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.002795734057268609</v>
+        <v>0.07060383409165563</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.03584555947100912</v>
+        <v>0.01682263222457325</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.00258541826303072</v>
+        <v>-0.01521958738026408</v>
       </c>
       <c r="EC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.08593620734471746</v>
+        <v>-0.114526649424992</v>
       </c>
       <c r="EH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.03471547948101402</v>
+        <v>0.07162425893107426</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.0367353333852423</v>
+        <v>-0.1009926891466333</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.008353643140979465</v>
+        <v>-0.02670890678746801</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.03584935300058535</v>
+        <v>-0.09565654023149291</v>
       </c>
       <c r="EQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.0003255704418690113</v>
+        <v>-0.08395119485912086</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.004785980301531378</v>
+        <v>-0.07426719753134392</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.06831097152479307</v>
+        <v>0.2493991858716779</v>
       </c>
       <c r="EU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV9" t="n">
         <v>0</v>
       </c>
       <c r="EW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.04709916610512214</v>
+        <v>-0.2822239029585729</v>
       </c>
       <c r="EZ9" t="n">
         <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.00705408079461627</v>
+        <v>0.0427143634043378</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.01414332293081877</v>
+        <v>-0.1164456146798406</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.04210197371695123</v>
+        <v>0.08940379044054639</v>
       </c>
       <c r="FD9" t="n">
         <v>0</v>
       </c>
       <c r="FE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.03531574651317242</v>
+        <v>-0.2221661969964162</v>
       </c>
       <c r="FI9" t="n">
         <v>-0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.03391435740103591</v>
+        <v>0.1418176003039721</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.003532563844474296</v>
+        <v>-0.03954314121581561</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.00800320829410152</v>
+        <v>0.3488679216806419</v>
       </c>
       <c r="FM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO9" t="n">
         <v>0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.006610866519397472</v>
+        <v>-0.1847785072457316</v>
       </c>
       <c r="FR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.01631024947911528</v>
+        <v>0.2851599745447508</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.006098666960557544</v>
+        <v>0.006130310389735823</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.0003246674849548178</v>
+        <v>0.08912753497891127</v>
       </c>
       <c r="FV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW9" t="n">
         <v>-0</v>
       </c>
       <c r="FX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.03548492396418154</v>
+        <v>-0.09927253597834998</v>
       </c>
       <c r="GA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB9" t="n">
-        <v>-0.02308780334112119</v>
+        <v>-0.194549181245576</v>
       </c>
       <c r="GC9" t="n">
         <v>-0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0.001559574311184672</v>
+        <v>-0.08116691836157176</v>
       </c>
       <c r="GE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -6120,10 +6120,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.6333321328806398</v>
+        <v>-0.2084792159555122</v>
       </c>
       <c r="C11" t="n">
         <v>-0</v>
@@ -6132,13 +6132,13 @@
         <v>-0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1440645318562985</v>
+        <v>-0.006384425030151558</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9478170162920985</v>
+        <v>0.189834941200862</v>
       </c>
       <c r="G11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -6147,10 +6147,10 @@
         <v>-0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.2768047235892421</v>
+        <v>-0.1096166751430972</v>
       </c>
       <c r="L11" t="n">
         <v>-0</v>
@@ -6159,10 +6159,10 @@
         <v>-0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.04714759552105241</v>
+        <v>0.04994366285250167</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6130080528745286</v>
+        <v>0.1275513823510485</v>
       </c>
       <c r="P11" t="n">
         <v>-0</v>
@@ -6177,22 +6177,22 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.08987364958049784</v>
+        <v>-0.07447894772877092</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V11" t="n">
         <v>-0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.09929075318987055</v>
+        <v>-0.01028612858590421</v>
       </c>
       <c r="X11" t="n">
-        <v>0.01322540642381054</v>
+        <v>-0.03034365880860297</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
@@ -6201,10 +6201,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.2292662844646398</v>
+        <v>0.04934224178435086</v>
       </c>
       <c r="AD11" t="n">
         <v>-0</v>
@@ -6213,10 +6213,10 @@
         <v>-0</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.009041921356546138</v>
+        <v>0.1325664531607018</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.1794684588853131</v>
+        <v>0.02895627485620352</v>
       </c>
       <c r="AH11" t="n">
         <v>-0</v>
@@ -6231,22 +6231,22 @@
         <v>-0</v>
       </c>
       <c r="AL11" t="n">
-        <v>-0.1023697505229313</v>
+        <v>-0.1064408785403294</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.133995609998641</v>
+        <v>-0.06988470441452106</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.2848560101649846</v>
+        <v>0.1473352732760574</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -6258,7 +6258,7 @@
         <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>-0.3965576578619361</v>
+        <v>-0.2712167576070214</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -6267,25 +6267,25 @@
         <v>-0</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.3715169595648701</v>
+        <v>0.08545254241921577</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.898446928044848</v>
+        <v>0.1229258411756775</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
         <v>-0</v>
       </c>
       <c r="BD11" t="n">
-        <v>-0.407520166372013</v>
+        <v>0.08502860584449448</v>
       </c>
       <c r="BE11" t="n">
         <v>-0</v>
@@ -6294,25 +6294,25 @@
         <v>-0</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.1853226290135963</v>
+        <v>0.1992327461192683</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.1937053163495445</v>
+        <v>0.1106634423137898</v>
       </c>
       <c r="BI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM11" t="n">
-        <v>-0.1100656542514048</v>
+        <v>0.01639344190314307</v>
       </c>
       <c r="BN11" t="n">
         <v>0</v>
@@ -6321,10 +6321,10 @@
         <v>0</v>
       </c>
       <c r="BP11" t="n">
-        <v>-0.1007975938249138</v>
+        <v>-0.05520747974159876</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.003827582056926658</v>
+        <v>-0.04510861521099055</v>
       </c>
       <c r="BR11" t="n">
         <v>0</v>
@@ -6339,25 +6339,25 @@
         <v>0</v>
       </c>
       <c r="BV11" t="n">
-        <v>-0.2135037216207077</v>
+        <v>-0.2043496119656293</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX11" t="n">
         <v>-0</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.1011905607977777</v>
+        <v>0.004108661655667133</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.3343115544923815</v>
+        <v>0.08431087855857648</v>
       </c>
       <c r="CA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC11" t="n">
         <v>-0</v>
@@ -6366,7 +6366,7 @@
         <v>0</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.1917405269793536</v>
+        <v>0.1225254342914704</v>
       </c>
       <c r="CF11" t="n">
         <v>0</v>
@@ -6375,10 +6375,10 @@
         <v>0</v>
       </c>
       <c r="CH11" t="n">
-        <v>-0.01392885338782887</v>
+        <v>-0.01319583423710121</v>
       </c>
       <c r="CI11" t="n">
-        <v>-0.1923463616915325</v>
+        <v>-0.07743273012909681</v>
       </c>
       <c r="CJ11" t="n">
         <v>0</v>
@@ -6387,28 +6387,28 @@
         <v>-0</v>
       </c>
       <c r="CL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM11" t="n">
         <v>-0</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.01870983651228235</v>
+        <v>0.0735202445044103</v>
       </c>
       <c r="CO11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP11" t="n">
         <v>0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.2128664555115923</v>
+        <v>-0.1443724349365737</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.1178104982967436</v>
+        <v>-0.04107696025664406</v>
       </c>
       <c r="CS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT11" t="n">
         <v>0</v>
@@ -6417,10 +6417,10 @@
         <v>0</v>
       </c>
       <c r="CV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.1588111466996637</v>
+        <v>0.1107408049406598</v>
       </c>
       <c r="CX11" t="n">
         <v>-0</v>
@@ -6429,10 +6429,10 @@
         <v>-0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>-0.06267377383661794</v>
+        <v>-0.01041636696222213</v>
       </c>
       <c r="DA11" t="n">
-        <v>-0.2316167622665714</v>
+        <v>-0.06522510937247344</v>
       </c>
       <c r="DB11" t="n">
         <v>-0</v>
@@ -6447,52 +6447,52 @@
         <v>-0</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.01400185717823196</v>
+        <v>-0.003995657365040254</v>
       </c>
       <c r="DG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH11" t="n">
         <v>0</v>
       </c>
       <c r="DI11" t="n">
-        <v>-0.2584495789923995</v>
+        <v>0.0498187860226145</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.03326402031973864</v>
+        <v>-0.01065246494434375</v>
       </c>
       <c r="DK11" t="n">
         <v>-0</v>
       </c>
       <c r="DL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.1236803356152932</v>
+        <v>0.02124188153493036</v>
       </c>
       <c r="DP11" t="n">
         <v>0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.1041139570545863</v>
+        <v>0.007669797168659903</v>
       </c>
       <c r="DS11" t="n">
-        <v>-0.06952409350688951</v>
+        <v>-0.02506587373349488</v>
       </c>
       <c r="DT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV11" t="n">
         <v>0</v>
@@ -6501,7 +6501,7 @@
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>-0.1309708494361494</v>
+        <v>-0.03391614190114071</v>
       </c>
       <c r="DY11" t="n">
         <v>0</v>
@@ -6510,10 +6510,10 @@
         <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.2929865533099328</v>
+        <v>0.0497579787310474</v>
       </c>
       <c r="EB11" t="n">
-        <v>-0.1000511045917228</v>
+        <v>0.02212487484629061</v>
       </c>
       <c r="EC11" t="n">
         <v>0</v>
@@ -6522,25 +6522,25 @@
         <v>-0</v>
       </c>
       <c r="EE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF11" t="n">
         <v>-0</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.0793975541923761</v>
+        <v>0.05819865071308115</v>
       </c>
       <c r="EH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>-0.1459935794740662</v>
+        <v>0.01846939864496878</v>
       </c>
       <c r="EK11" t="n">
-        <v>-0.1644080759119566</v>
+        <v>-0.01011193822996479</v>
       </c>
       <c r="EL11" t="n">
         <v>0</v>
@@ -6549,13 +6549,13 @@
         <v>-0</v>
       </c>
       <c r="EN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.1711079067931622</v>
+        <v>0.09367782183312537</v>
       </c>
       <c r="EQ11" t="n">
         <v>0</v>
@@ -6564,25 +6564,25 @@
         <v>-0</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.08809072694169402</v>
+        <v>0.07162776965567434</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.006277793455702759</v>
+        <v>0.09626699634157608</v>
       </c>
       <c r="EU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.178110070323006</v>
+        <v>0.1272744353608633</v>
       </c>
       <c r="EZ11" t="n">
         <v>0</v>
@@ -6591,13 +6591,13 @@
         <v>0</v>
       </c>
       <c r="FB11" t="n">
-        <v>-0.05886863043145255</v>
+        <v>-0.003162623344727291</v>
       </c>
       <c r="FC11" t="n">
-        <v>-0.2320116557213362</v>
+        <v>-0.06032154245826478</v>
       </c>
       <c r="FD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE11" t="n">
         <v>-0</v>
@@ -6606,10 +6606,10 @@
         <v>0</v>
       </c>
       <c r="FG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.01800079849460328</v>
+        <v>0.1259115030178628</v>
       </c>
       <c r="FI11" t="n">
         <v>-0</v>
@@ -6618,37 +6618,37 @@
         <v>0</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.01501975987369351</v>
+        <v>-0.04267275441389723</v>
       </c>
       <c r="FL11" t="n">
-        <v>-0.2392463723158225</v>
+        <v>-0.0993115145385092</v>
       </c>
       <c r="FM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN11" t="n">
         <v>-0</v>
       </c>
       <c r="FO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.008423739451268418</v>
+        <v>0.1100794135240663</v>
       </c>
       <c r="FR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS11" t="n">
         <v>0</v>
       </c>
       <c r="FT11" t="n">
-        <v>-0.1484080108072988</v>
+        <v>-0.01005489410683047</v>
       </c>
       <c r="FU11" t="n">
-        <v>-0.3303382599966145</v>
+        <v>-0.07058023032862215</v>
       </c>
       <c r="FV11" t="n">
         <v>0</v>
@@ -6663,10 +6663,10 @@
         <v>-0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.1283005601406513</v>
+        <v>0.113629337868941</v>
       </c>
       <c r="GA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB11" t="n">
         <v>0</v>
@@ -6675,7 +6675,7 @@
         <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.0872130603933849</v>
+        <v>0.03830205089082456</v>
       </c>
       <c r="GE11" t="n">
         <v>0</v>
@@ -6689,22 +6689,22 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.1333747704097537</v>
+        <v>0.5148325973131788</v>
       </c>
       <c r="C12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.006346353310403234</v>
+        <v>0.0002700440850149603</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.09238705329937291</v>
+        <v>-0.280564342159551</v>
       </c>
       <c r="G12" t="n">
         <v>-0</v>
@@ -6716,10 +6716,10 @@
         <v>-0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1074339899046069</v>
+        <v>0.6075606347199339</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -6728,16 +6728,16 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.004922750975620268</v>
+        <v>-0.1269468041886106</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.06333348995726427</v>
+        <v>-0.1982353532227623</v>
       </c>
       <c r="P12" t="n">
         <v>-0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>-0</v>
@@ -6746,7 +6746,7 @@
         <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.007850565653307266</v>
+        <v>0.1139995950450614</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
@@ -6755,16 +6755,16 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.01521090670274852</v>
+        <v>-0.004443227824983744</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.01571716032506547</v>
+        <v>-0.1177768790472474</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -6773,19 +6773,19 @@
         <v>-0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.008316099349665495</v>
+        <v>0.03215875159809943</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.01235721675422421</v>
+        <v>-0.06130712917934466</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.01731685655992342</v>
+        <v>0.07795744972795222</v>
       </c>
       <c r="AH12" t="n">
         <v>0</v>
@@ -6800,22 +6800,22 @@
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.006742006836319209</v>
+        <v>0.1657124953135528</v>
       </c>
       <c r="AM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
         <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.008719181063579343</v>
+        <v>0.06451357517745945</v>
       </c>
       <c r="AP12" t="n">
-        <v>-0.04350250535089837</v>
+        <v>-0.09482639186049169</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR12" t="n">
         <v>-0</v>
@@ -6824,37 +6824,37 @@
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.1091571088354197</v>
+        <v>0.7338388647635505</v>
       </c>
       <c r="AV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.00885172471062848</v>
+        <v>-0.2759153201846885</v>
       </c>
       <c r="AY12" t="n">
-        <v>-0.06423155134413359</v>
+        <v>-0.3212020212138874</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA12" t="n">
         <v>-0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC12" t="n">
         <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.05188276019307981</v>
+        <v>-0.1839698045602423</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
@@ -6863,10 +6863,10 @@
         <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.02485971350127424</v>
+        <v>0.01335580953829206</v>
       </c>
       <c r="BH12" t="n">
-        <v>-0.05555194651347658</v>
+        <v>-0.0419011910793562</v>
       </c>
       <c r="BI12" t="n">
         <v>-0</v>
@@ -6875,52 +6875,52 @@
         <v>0</v>
       </c>
       <c r="BK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.03996804065148661</v>
+        <v>0.009174731277238977</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO12" t="n">
         <v>-0</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.01419698175298306</v>
+        <v>0.089843474575002</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.01794783304865634</v>
+        <v>0.04391066948069087</v>
       </c>
       <c r="BR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
         <v>-0</v>
       </c>
       <c r="BT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.05605944782850338</v>
+        <v>0.4384048668309342</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
         <v>0</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.002626131867736737</v>
+        <v>-0.03677873754959628</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0.02406693501916508</v>
+        <v>-0.1703999915772176</v>
       </c>
       <c r="CA12" t="n">
         <v>-0</v>
@@ -6935,25 +6935,25 @@
         <v>0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.02983591228312463</v>
+        <v>-0.2394700460300695</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
         <v>-0</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.00271046045514352</v>
+        <v>0.017515858575498</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.02423289219041722</v>
+        <v>0.1075699391986752</v>
       </c>
       <c r="CJ12" t="n">
         <v>0</v>
       </c>
       <c r="CK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL12" t="n">
         <v>0</v>
@@ -6962,61 +6962,61 @@
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.008574699962323611</v>
+        <v>-0.09829052415643967</v>
       </c>
       <c r="CO12" t="n">
         <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.00351575685253533</v>
+        <v>0.07772980135248647</v>
       </c>
       <c r="CR12" t="n">
-        <v>-0.008853434160957165</v>
+        <v>0.04492254828031166</v>
       </c>
       <c r="CS12" t="n">
         <v>-0</v>
       </c>
       <c r="CT12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV12" t="n">
         <v>-0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.0223002523975217</v>
+        <v>-0.2237061299253223</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
         <v>0</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.0022845470218262</v>
+        <v>0.01441453771117305</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.02978972586931386</v>
+        <v>0.1233328294515248</v>
       </c>
       <c r="DB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.004042153493190569</v>
+        <v>0.01108555135666103</v>
       </c>
       <c r="DG12" t="n">
         <v>0</v>
@@ -7025,10 +7025,10 @@
         <v>-0</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.008102356115746018</v>
+        <v>0.02229123519137749</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.0126818434258586</v>
+        <v>0.09452965097261611</v>
       </c>
       <c r="DK12" t="n">
         <v>0</v>
@@ -7040,28 +7040,28 @@
         <v>0</v>
       </c>
       <c r="DN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.0117108452349807</v>
+        <v>-0.08465824679981289</v>
       </c>
       <c r="DP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.007697112199631012</v>
+        <v>-0.0183323931389147</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.004775339957483572</v>
+        <v>0.08594244480854549</v>
       </c>
       <c r="DT12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV12" t="n">
         <v>0</v>
@@ -7070,46 +7070,46 @@
         <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>-0.03625581567067365</v>
+        <v>-0.1572603468630954</v>
       </c>
       <c r="DY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ12" t="n">
         <v>-0</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.009218750434680942</v>
+        <v>0.06259317427101001</v>
       </c>
       <c r="EB12" t="n">
-        <v>-0.01784494534518465</v>
+        <v>-0.1024368562931136</v>
       </c>
       <c r="EC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.02071768898491964</v>
+        <v>-0.1283539480535044</v>
       </c>
       <c r="EH12" t="n">
         <v>-0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.003104876901817064</v>
+        <v>-0.05031721999726278</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.0156409895730309</v>
+        <v>0.0412747467355729</v>
       </c>
       <c r="EL12" t="n">
         <v>-0</v>
@@ -7124,19 +7124,19 @@
         <v>0</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.007571463270012959</v>
+        <v>0.0938704795640192</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
         <v>-0</v>
       </c>
       <c r="ES12" t="n">
-        <v>-0.003932367996226053</v>
+        <v>0.0142643575323563</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.001880821807891714</v>
+        <v>-0.04128950148844369</v>
       </c>
       <c r="EU12" t="n">
         <v>0</v>
@@ -7145,52 +7145,52 @@
         <v>0</v>
       </c>
       <c r="EW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX12" t="n">
         <v>0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.02198731072545749</v>
+        <v>-0.2578804784633106</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA12" t="n">
         <v>-0</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.001206428374172076</v>
+        <v>-0.007625591026963668</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.03021805443850384</v>
+        <v>0.1250087453308819</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
         <v>0</v>
       </c>
       <c r="FF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG12" t="n">
         <v>0</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.003380217103684103</v>
+        <v>-0.1260089855804763</v>
       </c>
       <c r="FI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ12" t="n">
         <v>-0</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.01607362177234817</v>
+        <v>-0.01451814246354441</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.02992896954521935</v>
+        <v>0.1362518640586858</v>
       </c>
       <c r="FM12" t="n">
         <v>-0</v>
@@ -7205,7 +7205,7 @@
         <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.0196555951489811</v>
+        <v>-0.2368096317537156</v>
       </c>
       <c r="FR12" t="n">
         <v>-0</v>
@@ -7214,37 +7214,37 @@
         <v>-0</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.02443977178562185</v>
+        <v>-0.06122378289717301</v>
       </c>
       <c r="FU12" t="n">
-        <v>-0.0008763209283351258</v>
+        <v>-0.0101744704646738</v>
       </c>
       <c r="FV12" t="n">
         <v>-0</v>
       </c>
       <c r="FW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX12" t="n">
         <v>0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.01311891922634132</v>
+        <v>-0.1134967812113027</v>
       </c>
       <c r="GA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0.02613882249697758</v>
+        <v>0.07198302679113594</v>
       </c>
       <c r="GE12" t="n">
         <v>-0</v>
@@ -7253,7 +7253,7 @@
         <v>-0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -7261,16 +7261,16 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.3595239659945326</v>
+        <v>-0.3737637328004914</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1918948061953517</v>
+        <v>0.1326478602353585</v>
       </c>
       <c r="E13" t="n">
-        <v>0.217961686878524</v>
+        <v>0.07984689236739811</v>
       </c>
       <c r="F13" t="n">
         <v>-0</v>
@@ -7282,25 +7282,25 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.290603672443886</v>
+        <v>-0.4559974253514154</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2105292914795927</v>
+        <v>0.223032096262105</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2389788726610567</v>
+        <v>0.1539367503506809</v>
       </c>
       <c r="O13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -7315,25 +7315,25 @@
         <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1015994294792082</v>
+        <v>-0.0402388324492669</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>0.01694052201451101</v>
+        <v>0.01267256161566748</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.04183647001244236</v>
+        <v>-0.005544661424828436</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
         <v>-0</v>
@@ -7342,22 +7342,22 @@
         <v>-0</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.1524543817303817</v>
+        <v>-0.01986218768638529</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0.05730643156480612</v>
+        <v>0.1338706937573633</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.03112473842292171</v>
+        <v>-0.2222037577602377</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -7366,76 +7366,76 @@
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>-0.03530618224662264</v>
+        <v>-0.1467362683141169</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.04496369266459647</v>
+        <v>0.03771858075953894</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.07773047799036843</v>
+        <v>-0.2313778420852493</v>
       </c>
       <c r="AP13" t="n">
         <v>-0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
         <v>-0</v>
       </c>
       <c r="AS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
         <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>-0.2823760744888923</v>
+        <v>-0.2428530737293749</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.009386233642463646</v>
+        <v>0.140834232216819</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.01912585227520819</v>
+        <v>0.02256290232743481</v>
       </c>
       <c r="AY13" t="n">
         <v>-0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.01270378074326078</v>
+        <v>0.05066757266978159</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.1947370835745189</v>
+        <v>0.01267303549555298</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.2801864307627785</v>
+        <v>0.131204742198662</v>
       </c>
       <c r="BH13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI13" t="n">
         <v>-0</v>
@@ -7450,16 +7450,16 @@
         <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>-0.09746939744970234</v>
+        <v>0.1121550478169164</v>
       </c>
       <c r="BN13" t="n">
         <v>0</v>
       </c>
       <c r="BO13" t="n">
-        <v>-0.03966367599017617</v>
+        <v>0.08290456634644046</v>
       </c>
       <c r="BP13" t="n">
-        <v>-0.1006469971429728</v>
+        <v>0.001854649371135884</v>
       </c>
       <c r="BQ13" t="n">
         <v>0</v>
@@ -7477,25 +7477,25 @@
         <v>0</v>
       </c>
       <c r="BV13" t="n">
-        <v>-0.2214552231237848</v>
+        <v>-0.1967383025962886</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.001954980983664282</v>
+        <v>0.06910249671461589</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.04295490695730891</v>
+        <v>-0.0085159241749709</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC13" t="n">
         <v>-0</v>
@@ -7504,25 +7504,25 @@
         <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.09111559250187642</v>
+        <v>0.1941410410625169</v>
       </c>
       <c r="CF13" t="n">
         <v>0</v>
       </c>
       <c r="CG13" t="n">
-        <v>-0.04630099311145542</v>
+        <v>-0.05770707510185234</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.002501104486842532</v>
+        <v>-0.004755495526076575</v>
       </c>
       <c r="CI13" t="n">
         <v>0</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL13" t="n">
         <v>0</v>
@@ -7531,19 +7531,19 @@
         <v>-0</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.03036194770759994</v>
+        <v>0.089814116304601</v>
       </c>
       <c r="CO13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP13" t="n">
-        <v>-0.06177633397348618</v>
+        <v>-0.08566313376769037</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.08264093758651204</v>
+        <v>-0.03688885645439984</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS13" t="n">
         <v>0</v>
@@ -7558,22 +7558,22 @@
         <v>0</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.08768772856841285</v>
+        <v>0.203680935099142</v>
       </c>
       <c r="CX13" t="n">
         <v>-0</v>
       </c>
       <c r="CY13" t="n">
-        <v>-0.06427216599515229</v>
+        <v>-0.05883352196937213</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.003251567564702623</v>
+        <v>-0.03258943965871855</v>
       </c>
       <c r="DA13" t="n">
         <v>-0</v>
       </c>
       <c r="DB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC13" t="n">
         <v>-0</v>
@@ -7585,52 +7585,52 @@
         <v>-0</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.1674791704590838</v>
+        <v>0.1516227042501961</v>
       </c>
       <c r="DG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0.05120534549396998</v>
+        <v>-0.02342471104732869</v>
       </c>
       <c r="DI13" t="n">
-        <v>-0.008569236863323306</v>
+        <v>-0.000970404644517681</v>
       </c>
       <c r="DJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL13" t="n">
         <v>-0</v>
       </c>
       <c r="DM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.0444027720261606</v>
+        <v>0.09032915425264003</v>
       </c>
       <c r="DP13" t="n">
         <v>0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.03951346969164644</v>
+        <v>-0.04203099856430466</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.06924336164510286</v>
+        <v>0.02707078849941816</v>
       </c>
       <c r="DS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT13" t="n">
         <v>0</v>
       </c>
       <c r="DU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV13" t="n">
         <v>-0</v>
@@ -7639,22 +7639,22 @@
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.1020258637098203</v>
+        <v>0.04218837314236253</v>
       </c>
       <c r="DY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>-0.09150862549650279</v>
+        <v>0.04949671606083903</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.05065278254419057</v>
+        <v>0.006867971764129158</v>
       </c>
       <c r="EB13" t="n">
         <v>0</v>
       </c>
       <c r="EC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED13" t="n">
         <v>-0</v>
@@ -7666,22 +7666,22 @@
         <v>-0</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.05382829121024003</v>
+        <v>0.2267285513372236</v>
       </c>
       <c r="EH13" t="n">
         <v>-0</v>
       </c>
       <c r="EI13" t="n">
-        <v>-0.04169300521635982</v>
+        <v>-0.0568662035802833</v>
       </c>
       <c r="EJ13" t="n">
-        <v>-0.1036737619249987</v>
+        <v>-0.03789969876844101</v>
       </c>
       <c r="EK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM13" t="n">
         <v>0</v>
@@ -7690,28 +7690,28 @@
         <v>0</v>
       </c>
       <c r="EO13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.0004639062558998706</v>
+        <v>-0.1168263580159574</v>
       </c>
       <c r="EQ13" t="n">
         <v>0</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.03281302057021471</v>
+        <v>-0.01012929929656321</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.02831961310528018</v>
+        <v>0.004782772460820705</v>
       </c>
       <c r="ET13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU13" t="n">
         <v>-0</v>
       </c>
       <c r="EV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW13" t="n">
         <v>0</v>
@@ -7720,16 +7720,16 @@
         <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.09068410370469708</v>
+        <v>0.2302553806432373</v>
       </c>
       <c r="EZ13" t="n">
         <v>0</v>
       </c>
       <c r="FA13" t="n">
-        <v>-0.05954802278726774</v>
+        <v>-0.0707934113191805</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.005773934316406578</v>
+        <v>-0.0006280483128592738</v>
       </c>
       <c r="FC13" t="n">
         <v>0</v>
@@ -7738,52 +7738,52 @@
         <v>-0</v>
       </c>
       <c r="FE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG13" t="n">
         <v>-0</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.05169731641457217</v>
+        <v>0.08428186888562736</v>
       </c>
       <c r="FI13" t="n">
         <v>0</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.08810583646586569</v>
+        <v>0.1085450814762721</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.04179208425015184</v>
+        <v>0.03676015370198812</v>
       </c>
       <c r="FL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.02522769737549652</v>
+        <v>0.1785516605937419</v>
       </c>
       <c r="FR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.03322027598198776</v>
+        <v>0.01260390136827294</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.009205554983633504</v>
+        <v>-0.05637390529607172</v>
       </c>
       <c r="FU13" t="n">
         <v>0</v>
@@ -7792,37 +7792,37 @@
         <v>-0</v>
       </c>
       <c r="FW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX13" t="n">
         <v>-0</v>
       </c>
       <c r="FY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.05225639164725931</v>
+        <v>0.2022148667834</v>
       </c>
       <c r="GA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.06616922842704878</v>
+        <v>-0.001531745628289719</v>
       </c>
       <c r="GC13" t="n">
         <v>-0</v>
       </c>
       <c r="GD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE13" t="n">
         <v>0</v>
       </c>
       <c r="GF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -7830,7 +7830,7 @@
         <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>0.4870340664615532</v>
+        <v>0.3451182324101872</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -7839,16 +7839,16 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1171038079518017</v>
+        <v>-0.02415007276200525</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4436249964418046</v>
+        <v>-0.1423975481477552</v>
       </c>
       <c r="G14" t="n">
         <v>-0</v>
       </c>
       <c r="H14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.4564442769178869</v>
+        <v>0.4556398729406052</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -7866,25 +7866,25 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.05570592675916219</v>
+        <v>-0.1057542333602102</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.4518573142021146</v>
+        <v>-0.2037387679502438</v>
       </c>
       <c r="P14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.03678668043720053</v>
+        <v>0.0994621737550056</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -7893,16 +7893,16 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.08439262822239568</v>
+        <v>-0.1181451646230026</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.01567068857811676</v>
+        <v>-0.01165391202914747</v>
       </c>
       <c r="Y14" t="n">
         <v>-0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -7911,19 +7911,19 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0.02363507836424826</v>
+        <v>-0.03181093238320283</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.01012467495818293</v>
+        <v>-0.2802260515972894</v>
       </c>
       <c r="AG14" t="n">
-        <v>-0.03447034086699631</v>
+        <v>-0.0004806981102348303</v>
       </c>
       <c r="AH14" t="n">
         <v>-0</v>
@@ -7938,7 +7938,7 @@
         <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.08346482370634739</v>
+        <v>0.03391320067782991</v>
       </c>
       <c r="AM14" t="n">
         <v>-0</v>
@@ -7947,10 +7947,10 @@
         <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.001425139274130004</v>
+        <v>-0.04382687751844315</v>
       </c>
       <c r="AP14" t="n">
-        <v>-0.08288815890890448</v>
+        <v>0.01800998439388342</v>
       </c>
       <c r="AQ14" t="n">
         <v>-0</v>
@@ -7962,10 +7962,10 @@
         <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.4142823062989933</v>
+        <v>0.490930550772916</v>
       </c>
       <c r="AV14" t="n">
         <v>-0</v>
@@ -7974,16 +7974,16 @@
         <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>-0.07056162875261536</v>
+        <v>-0.2412630341333792</v>
       </c>
       <c r="AY14" t="n">
-        <v>-0.2195072107427806</v>
+        <v>-0.1060183635823349</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
         <v>0</v>
@@ -7992,7 +7992,7 @@
         <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.1084983479853896</v>
+        <v>-0.03244371999040717</v>
       </c>
       <c r="BE14" t="n">
         <v>0</v>
@@ -8001,52 +8001,52 @@
         <v>0</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.1511296373082835</v>
+        <v>-0.01743696709524062</v>
       </c>
       <c r="BH14" t="n">
-        <v>-0.1920463743209763</v>
+        <v>-0.08854328880803962</v>
       </c>
       <c r="BI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK14" t="n">
         <v>0</v>
       </c>
       <c r="BL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.1430673738132707</v>
+        <v>0.0555858806580355</v>
       </c>
       <c r="BN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO14" t="n">
         <v>-0</v>
       </c>
       <c r="BP14" t="n">
-        <v>-0.003506804419984493</v>
+        <v>0.08095184223925117</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.01774829638850664</v>
+        <v>-0.0353695774531211</v>
       </c>
       <c r="BR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU14" t="n">
         <v>-0</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.2174578064331273</v>
+        <v>0.2645884054932645</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
@@ -8055,10 +8055,10 @@
         <v>0</v>
       </c>
       <c r="BY14" t="n">
-        <v>-0.07027843473932166</v>
+        <v>-0.07607225122038919</v>
       </c>
       <c r="BZ14" t="n">
-        <v>-0.1317131469424722</v>
+        <v>-0.1065766498934343</v>
       </c>
       <c r="CA14" t="n">
         <v>-0</v>
@@ -8073,22 +8073,22 @@
         <v>-0</v>
       </c>
       <c r="CE14" t="n">
-        <v>-0.08493679991571336</v>
+        <v>-0.1128628071677499</v>
       </c>
       <c r="CF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG14" t="n">
         <v>-0</v>
       </c>
       <c r="CH14" t="n">
-        <v>-0.005132296706541574</v>
+        <v>0.02940671068759908</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.107260316561954</v>
+        <v>0.05005876308788209</v>
       </c>
       <c r="CJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK14" t="n">
         <v>0</v>
@@ -8100,100 +8100,100 @@
         <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.411111576022698e-05</v>
+        <v>-0.1176648399683078</v>
       </c>
       <c r="CO14" t="n">
         <v>-0</v>
       </c>
       <c r="CP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.01656313510158922</v>
+        <v>0.0987659328249483</v>
       </c>
       <c r="CR14" t="n">
-        <v>-0.02173635870421967</v>
+        <v>0.09696302121904032</v>
       </c>
       <c r="CS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW14" t="n">
-        <v>-0.06794519309467903</v>
+        <v>-0.1132667735478171</v>
       </c>
       <c r="CX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY14" t="n">
         <v>0</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-0.002517826506811512</v>
+        <v>0.008266387471978583</v>
       </c>
       <c r="DA14" t="n">
-        <v>0.1129463761574095</v>
+        <v>0.07134993351079165</v>
       </c>
       <c r="DB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC14" t="n">
         <v>-0</v>
       </c>
       <c r="DD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>-0.04002326517017469</v>
+        <v>-0.04182103570936625</v>
       </c>
       <c r="DG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.0444566794875837</v>
+        <v>-0.1773522024170269</v>
       </c>
       <c r="DJ14" t="n">
-        <v>-0.001614683906987056</v>
+        <v>0.05430905562071246</v>
       </c>
       <c r="DK14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM14" t="n">
         <v>0</v>
       </c>
       <c r="DN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.006081052987154392</v>
+        <v>-0.006789881564130029</v>
       </c>
       <c r="DP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.03351720870604942</v>
+        <v>-0.06165173203514228</v>
       </c>
       <c r="DS14" t="n">
-        <v>-0.00651404814989466</v>
+        <v>0.07945600496514979</v>
       </c>
       <c r="DT14" t="n">
         <v>-0</v>
@@ -8202,13 +8202,13 @@
         <v>-0</v>
       </c>
       <c r="DV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW14" t="n">
         <v>-0</v>
       </c>
       <c r="DX14" t="n">
-        <v>-0.05777594466092893</v>
+        <v>-0.0203989119697206</v>
       </c>
       <c r="DY14" t="n">
         <v>0</v>
@@ -8217,106 +8217,106 @@
         <v>-0</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.01639577769065341</v>
+        <v>-0.0676568575607339</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.05440360332127209</v>
+        <v>0.03633715307927934</v>
       </c>
       <c r="EC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED14" t="n">
         <v>0</v>
       </c>
       <c r="EE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG14" t="n">
-        <v>-0.09693440032671177</v>
+        <v>-0.04598912915854268</v>
       </c>
       <c r="EH14" t="n">
         <v>0</v>
       </c>
       <c r="EI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.02439302318152298</v>
+        <v>0.02204225341916105</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.1195640580710318</v>
+        <v>-0.009853383573066175</v>
       </c>
       <c r="EL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM14" t="n">
         <v>-0</v>
       </c>
       <c r="EN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP14" t="n">
-        <v>-0.02990216264525762</v>
+        <v>-0.005227696832770167</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER14" t="n">
         <v>-0</v>
       </c>
       <c r="ES14" t="n">
-        <v>-0.01296633880913288</v>
+        <v>-0.01220162516658875</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.07094629067274934</v>
+        <v>0.1364584260180013</v>
       </c>
       <c r="EU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV14" t="n">
         <v>0</v>
       </c>
       <c r="EW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY14" t="n">
-        <v>-0.06543195927951648</v>
+        <v>-0.130932432158351</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA14" t="n">
         <v>-0</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.006229404879093165</v>
+        <v>-0.002061555924192711</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.1024537790435004</v>
+        <v>0.03987951912620769</v>
       </c>
       <c r="FD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG14" t="n">
         <v>0</v>
       </c>
       <c r="FH14" t="n">
-        <v>-0.002535719417640378</v>
+        <v>0.2075057372435904</v>
       </c>
       <c r="FI14" t="n">
         <v>-0</v>
@@ -8325,16 +8325,16 @@
         <v>-0</v>
       </c>
       <c r="FK14" t="n">
-        <v>-0.008508884200727705</v>
+        <v>-0.08888362194263089</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.05172385674770193</v>
+        <v>0.1169911234280748</v>
       </c>
       <c r="FM14" t="n">
         <v>0</v>
       </c>
       <c r="FN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO14" t="n">
         <v>0</v>
@@ -8343,46 +8343,46 @@
         <v>0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0.004963051982165477</v>
+        <v>0.01095474566180105</v>
       </c>
       <c r="FR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS14" t="n">
         <v>-0</v>
       </c>
       <c r="FT14" t="n">
-        <v>-0.008810654514323803</v>
+        <v>-0.02433236845990461</v>
       </c>
       <c r="FU14" t="n">
-        <v>0.03438754936987051</v>
+        <v>-0.04959525460895942</v>
       </c>
       <c r="FV14" t="n">
         <v>-0</v>
       </c>
       <c r="FW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.04462418624405818</v>
+        <v>-0.0392241248176862</v>
       </c>
       <c r="GA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD14" t="n">
-        <v>-0.05108333755087999</v>
+        <v>0.06229019800014492</v>
       </c>
       <c r="GE14" t="n">
         <v>-0</v>
@@ -8391,7 +8391,7 @@
         <v>-0</v>
       </c>
       <c r="GG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -9537,7 +9537,7 @@
         <v>0</v>
       </c>
       <c r="B17" t="n">
-        <v>0.1555227955103367</v>
+        <v>0.3740873085411197</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -9546,25 +9546,25 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.08280241633837762</v>
+        <v>-0.01212069175337799</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.07228254118439849</v>
+        <v>-0.1420221622722794</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1280013609926359</v>
+        <v>0.4550155857997566</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -9573,25 +9573,25 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.05768573777505789</v>
+        <v>-0.1030346101625517</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.07598714090533507</v>
+        <v>-0.1872297503630286</v>
       </c>
       <c r="P17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.01378244307605709</v>
+        <v>0.08850790259557874</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -9600,40 +9600,40 @@
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.004451178988662641</v>
+        <v>-0.08737791763617689</v>
       </c>
       <c r="X17" t="n">
-        <v>0.009296517155136153</v>
+        <v>-0.01195679459117023</v>
       </c>
       <c r="Y17" t="n">
         <v>-0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.004937052603166965</v>
+        <v>-0.03445648712941773</v>
       </c>
       <c r="AD17" t="n">
         <v>-0</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.01397086337945391</v>
+        <v>-0.2456376296061947</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.01246458326384953</v>
+        <v>0.01208147322881906</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI17" t="n">
         <v>-0</v>
@@ -9645,22 +9645,22 @@
         <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.01048426267962558</v>
+        <v>0.03864887039576933</v>
       </c>
       <c r="AM17" t="n">
         <v>-0</v>
       </c>
       <c r="AN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>-0.008843058167262783</v>
+        <v>-0.03478953138166604</v>
       </c>
       <c r="AP17" t="n">
-        <v>-0.01472490147678882</v>
+        <v>0.004348853773135694</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR17" t="n">
         <v>-0</v>
@@ -9669,28 +9669,28 @@
         <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.1072825700670186</v>
+        <v>0.4082565567656767</v>
       </c>
       <c r="AV17" t="n">
         <v>-0</v>
       </c>
       <c r="AW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>-0.02880010261672456</v>
+        <v>-0.2569226983256364</v>
       </c>
       <c r="AY17" t="n">
-        <v>-0.02119212093019258</v>
+        <v>-0.1019174011449789</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
         <v>0</v>
@@ -9699,7 +9699,7 @@
         <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.03149636970574076</v>
+        <v>-0.007966828915457077</v>
       </c>
       <c r="BE17" t="n">
         <v>0</v>
@@ -9708,52 +9708,52 @@
         <v>0</v>
       </c>
       <c r="BG17" t="n">
-        <v>-0.05775229627875221</v>
+        <v>0.003299825105484479</v>
       </c>
       <c r="BH17" t="n">
-        <v>-0.05909104473704765</v>
+        <v>-0.06672767056896817</v>
       </c>
       <c r="BI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK17" t="n">
         <v>0</v>
       </c>
       <c r="BL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.03556435611813727</v>
+        <v>0.03790515352353375</v>
       </c>
       <c r="BN17" t="n">
         <v>-0</v>
       </c>
       <c r="BO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.0160377211932141</v>
+        <v>0.05412149956945281</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0.01704690532514525</v>
+        <v>-0.02904912448350688</v>
       </c>
       <c r="BR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS17" t="n">
         <v>-0</v>
       </c>
       <c r="BT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.05103091105067987</v>
+        <v>0.2284431608214726</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
@@ -9762,10 +9762,10 @@
         <v>0</v>
       </c>
       <c r="BY17" t="n">
-        <v>-0.01218046926464564</v>
+        <v>-0.06484531704446789</v>
       </c>
       <c r="BZ17" t="n">
-        <v>-0.01384008897907786</v>
+        <v>-0.108101791999787</v>
       </c>
       <c r="CA17" t="n">
         <v>-0</v>
@@ -9774,31 +9774,31 @@
         <v>-0</v>
       </c>
       <c r="CC17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE17" t="n">
-        <v>-0.02622308846222178</v>
+        <v>-0.106248834828522</v>
       </c>
       <c r="CF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG17" t="n">
         <v>-0</v>
       </c>
       <c r="CH17" t="n">
-        <v>0.007127736093176795</v>
+        <v>0.02637823890535754</v>
       </c>
       <c r="CI17" t="n">
-        <v>0.01772200217820961</v>
+        <v>0.05235108424751526</v>
       </c>
       <c r="CJ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL17" t="n">
         <v>0</v>
@@ -9807,52 +9807,52 @@
         <v>0</v>
       </c>
       <c r="CN17" t="n">
-        <v>0.0008607606247808709</v>
+        <v>-0.1167963372686887</v>
       </c>
       <c r="CO17" t="n">
         <v>-0</v>
       </c>
       <c r="CP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ17" t="n">
-        <v>-0.007075855757484145</v>
+        <v>0.1418910920064637</v>
       </c>
       <c r="CR17" t="n">
-        <v>-0.01179765717120735</v>
+        <v>0.06948314519810558</v>
       </c>
       <c r="CS17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV17" t="n">
         <v>-0</v>
       </c>
       <c r="CW17" t="n">
-        <v>-0.01997228527183853</v>
+        <v>-0.1042914444843911</v>
       </c>
       <c r="CX17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY17" t="n">
         <v>0</v>
       </c>
       <c r="CZ17" t="n">
-        <v>0.006098553888960175</v>
+        <v>0.01336787605902164</v>
       </c>
       <c r="DA17" t="n">
-        <v>0.01817422480022265</v>
+        <v>0.07393732256271993</v>
       </c>
       <c r="DB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD17" t="n">
         <v>0</v>
@@ -9861,22 +9861,22 @@
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>-0.03236358042313904</v>
+        <v>-0.07613463879940778</v>
       </c>
       <c r="DG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.05139714038333401</v>
+        <v>-0.2088158290936235</v>
       </c>
       <c r="DJ17" t="n">
-        <v>0.01369322867674388</v>
+        <v>0.0664830782668345</v>
       </c>
       <c r="DK17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL17" t="n">
         <v>-0</v>
@@ -9885,28 +9885,28 @@
         <v>0</v>
       </c>
       <c r="DN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>-0.005787316285419271</v>
+        <v>-0.01453139399809695</v>
       </c>
       <c r="DP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ17" t="n">
         <v>0</v>
       </c>
       <c r="DR17" t="n">
-        <v>0.01937102480609069</v>
+        <v>-0.04380413370108927</v>
       </c>
       <c r="DS17" t="n">
-        <v>-0.009748317299426336</v>
+        <v>0.04598420032442908</v>
       </c>
       <c r="DT17" t="n">
         <v>-0</v>
       </c>
       <c r="DU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV17" t="n">
         <v>-0</v>
@@ -9915,49 +9915,49 @@
         <v>-0</v>
       </c>
       <c r="DX17" t="n">
-        <v>-0.02951577427682513</v>
+        <v>-0.008128724834928856</v>
       </c>
       <c r="DY17" t="n">
         <v>0</v>
       </c>
       <c r="DZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA17" t="n">
-        <v>0.01498315768491325</v>
+        <v>-0.05739258479727879</v>
       </c>
       <c r="EB17" t="n">
-        <v>0.01825960522851271</v>
+        <v>0.02186635189298738</v>
       </c>
       <c r="EC17" t="n">
         <v>-0</v>
       </c>
       <c r="ED17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG17" t="n">
-        <v>-0.0315053328593496</v>
+        <v>-0.04910027289638845</v>
       </c>
       <c r="EH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.00944317674849344</v>
+        <v>0.009966225733988959</v>
       </c>
       <c r="EK17" t="n">
-        <v>0.01334605781814872</v>
+        <v>-0.0008290111176221996</v>
       </c>
       <c r="EL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM17" t="n">
         <v>-0</v>
@@ -9966,82 +9966,82 @@
         <v>-0</v>
       </c>
       <c r="EO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP17" t="n">
-        <v>-0.01243019102766987</v>
+        <v>-0.03263751016830274</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER17" t="n">
         <v>-0</v>
       </c>
       <c r="ES17" t="n">
-        <v>0.002243096035829807</v>
+        <v>-0.01666909488296208</v>
       </c>
       <c r="ET17" t="n">
-        <v>-0.01165242559899074</v>
+        <v>0.1081606505080878</v>
       </c>
       <c r="EU17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV17" t="n">
         <v>0</v>
       </c>
       <c r="EW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY17" t="n">
-        <v>-0.0208915055260241</v>
+        <v>-0.1236182570442468</v>
       </c>
       <c r="EZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB17" t="n">
-        <v>0.009264301360075101</v>
+        <v>0.001119420975175839</v>
       </c>
       <c r="FC17" t="n">
-        <v>0.02170654796978215</v>
+        <v>0.04480882699908054</v>
       </c>
       <c r="FD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE17" t="n">
         <v>-0</v>
       </c>
       <c r="FF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG17" t="n">
         <v>0</v>
       </c>
       <c r="FH17" t="n">
-        <v>-0.01511337365004362</v>
+        <v>0.1682489665630392</v>
       </c>
       <c r="FI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ17" t="n">
         <v>-0</v>
       </c>
       <c r="FK17" t="n">
-        <v>0.0113268961668335</v>
+        <v>-0.08182097191585727</v>
       </c>
       <c r="FL17" t="n">
-        <v>0.01985781488408164</v>
+        <v>0.1168730928665216</v>
       </c>
       <c r="FM17" t="n">
         <v>0</v>
       </c>
       <c r="FN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO17" t="n">
         <v>0</v>
@@ -10050,63 +10050,63 @@
         <v>0</v>
       </c>
       <c r="FQ17" t="n">
-        <v>7.644719732458803e-05</v>
+        <v>0.001766033095943371</v>
       </c>
       <c r="FR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS17" t="n">
         <v>-0</v>
       </c>
       <c r="FT17" t="n">
-        <v>-0.001509859052916248</v>
+        <v>-0.008890543018079875</v>
       </c>
       <c r="FU17" t="n">
-        <v>0.01880918805336776</v>
+        <v>-0.02826654740530361</v>
       </c>
       <c r="FV17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ17" t="n">
-        <v>0.001820653164314721</v>
+        <v>-0.03526500023485375</v>
       </c>
       <c r="GA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB17" t="n">
         <v>-0</v>
       </c>
       <c r="GC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD17" t="n">
-        <v>-0.005457780234660795</v>
+        <v>0.06675703004937075</v>
       </c>
       <c r="GE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF17" t="n">
         <v>-0</v>
       </c>
       <c r="GG17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.1266462604957166</v>
+        <v>0.2568294364946774</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -10115,10 +10115,10 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0359596502453245</v>
+        <v>0.08360029537802897</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1458807809284861</v>
+        <v>-0.1124021230301778</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -10127,10 +10127,10 @@
         <v>-0</v>
       </c>
       <c r="I18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1005695273084039</v>
+        <v>0.2217196001047798</v>
       </c>
       <c r="K18" t="n">
         <v>-0</v>
@@ -10139,43 +10139,43 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.002737779122467324</v>
+        <v>-0.007165351043765546</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0997243053547566</v>
+        <v>-0.1079803910484537</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>-0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.01760666690443216</v>
+        <v>-0.06928175277144705</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.03898100455986269</v>
+        <v>-0.04621480493013201</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.02367567826519899</v>
+        <v>-0.08056909819103956</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
@@ -10184,7 +10184,7 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.01516222809156062</v>
+        <v>0.0545615304003013</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -10193,43 +10193,43 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>-0.02746700724001907</v>
+        <v>-0.03953367418522752</v>
       </c>
       <c r="AG18" t="n">
-        <v>-0.02875747820365326</v>
+        <v>0.05219803461472458</v>
       </c>
       <c r="AH18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK18" t="n">
-        <v>0.02170311454758471</v>
+        <v>0.01635961694893267</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>-0.007094937415410008</v>
+        <v>0.0310684134670413</v>
       </c>
       <c r="AP18" t="n">
-        <v>-0.01299687962429524</v>
+        <v>0.01725490832228489</v>
       </c>
       <c r="AQ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -10238,25 +10238,25 @@
         <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.08472652476482592</v>
+        <v>-0.0180578642833223</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AV18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
         <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>-0.1007914678233191</v>
+        <v>0.08887558904301493</v>
       </c>
       <c r="AY18" t="n">
-        <v>-0.08600565149370705</v>
+        <v>-0.007113253437926324</v>
       </c>
       <c r="AZ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
         <v>0</v>
@@ -10265,22 +10265,22 @@
         <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>0.01499549256361632</v>
+        <v>0.1617831854512066</v>
       </c>
       <c r="BD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF18" t="n">
         <v>0</v>
       </c>
       <c r="BG18" t="n">
-        <v>0.01190784752073141</v>
+        <v>-0.02019540684000256</v>
       </c>
       <c r="BH18" t="n">
-        <v>-0.04702454220862393</v>
+        <v>0.002295561210419389</v>
       </c>
       <c r="BI18" t="n">
         <v>0</v>
@@ -10292,10 +10292,10 @@
         <v>-0</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.007487808577764449</v>
+        <v>-0.06679451029213296</v>
       </c>
       <c r="BM18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BN18" t="n">
         <v>-0</v>
@@ -10304,37 +10304,37 @@
         <v>0</v>
       </c>
       <c r="BP18" t="n">
-        <v>0.003610416424803363</v>
+        <v>-0.1113391538630767</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0.008104688305153049</v>
+        <v>0.03653506681344443</v>
       </c>
       <c r="BR18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS18" t="n">
         <v>0</v>
       </c>
       <c r="BT18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU18" t="n">
-        <v>0.03643594286452657</v>
+        <v>-0.02642080760106553</v>
       </c>
       <c r="BV18" t="n">
         <v>0</v>
       </c>
       <c r="BW18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX18" t="n">
         <v>0</v>
       </c>
       <c r="BY18" t="n">
-        <v>-0.03598242985426318</v>
+        <v>-0.0702652693062062</v>
       </c>
       <c r="BZ18" t="n">
-        <v>-0.06421245250715174</v>
+        <v>-0.1104025499013803</v>
       </c>
       <c r="CA18" t="n">
         <v>-0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="CC18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD18" t="n">
-        <v>-0.02249073403637856</v>
+        <v>-0.06422544393623388</v>
       </c>
       <c r="CE18" t="n">
         <v>0</v>
@@ -10358,13 +10358,13 @@
         <v>0</v>
       </c>
       <c r="CH18" t="n">
-        <v>0.01066464430794283</v>
+        <v>0.007021126430780321</v>
       </c>
       <c r="CI18" t="n">
-        <v>0.04343561869056956</v>
+        <v>0.03115380220022167</v>
       </c>
       <c r="CJ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK18" t="n">
         <v>0</v>
@@ -10373,25 +10373,25 @@
         <v>-0</v>
       </c>
       <c r="CM18" t="n">
-        <v>0.004126862283695319</v>
+        <v>0.01181028276288585</v>
       </c>
       <c r="CN18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ18" t="n">
-        <v>0.06820944344543946</v>
+        <v>0.08373939567032432</v>
       </c>
       <c r="CR18" t="n">
-        <v>0.001346799260798693</v>
+        <v>-0.04380478783386278</v>
       </c>
       <c r="CS18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT18" t="n">
         <v>-0</v>
@@ -10400,7 +10400,7 @@
         <v>-0</v>
       </c>
       <c r="CV18" t="n">
-        <v>-0.02108001772460196</v>
+        <v>-0.06726026660128644</v>
       </c>
       <c r="CW18" t="n">
         <v>-0</v>
@@ -10412,40 +10412,40 @@
         <v>-0</v>
       </c>
       <c r="CZ18" t="n">
-        <v>0.01460815439289092</v>
+        <v>0.004563328884568592</v>
       </c>
       <c r="DA18" t="n">
-        <v>0.03937246904179714</v>
+        <v>0.03598994833441783</v>
       </c>
       <c r="DB18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC18" t="n">
         <v>-0</v>
       </c>
       <c r="DD18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE18" t="n">
-        <v>-0.0001534932277220459</v>
+        <v>-0.005146031250466448</v>
       </c>
       <c r="DF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DG18" t="n">
         <v>-0</v>
       </c>
       <c r="DH18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.03079357996395915</v>
+        <v>-0.06032322361351384</v>
       </c>
       <c r="DJ18" t="n">
-        <v>0.001550474019576347</v>
+        <v>0.01431398112090277</v>
       </c>
       <c r="DK18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL18" t="n">
         <v>0</v>
@@ -10454,7 +10454,7 @@
         <v>0</v>
       </c>
       <c r="DN18" t="n">
-        <v>-0.0005372762060466832</v>
+        <v>-0.03987372890085466</v>
       </c>
       <c r="DO18" t="n">
         <v>0</v>
@@ -10463,13 +10463,13 @@
         <v>0</v>
       </c>
       <c r="DQ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR18" t="n">
-        <v>0.03730876190525402</v>
+        <v>-0.05332094162376333</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.01723860783134225</v>
+        <v>0.08169112504517606</v>
       </c>
       <c r="DT18" t="n">
         <v>-0</v>
@@ -10478,37 +10478,37 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW18" t="n">
-        <v>-0.008746059748456648</v>
+        <v>0.02465871043844876</v>
       </c>
       <c r="DX18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DY18" t="n">
         <v>-0</v>
       </c>
       <c r="DZ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA18" t="n">
-        <v>0.01650795672862657</v>
+        <v>0.1237911810008313</v>
       </c>
       <c r="EB18" t="n">
-        <v>0.03860945368572078</v>
+        <v>0.06352424167544639</v>
       </c>
       <c r="EC18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE18" t="n">
         <v>0</v>
       </c>
       <c r="EF18" t="n">
-        <v>-0.02203262574153988</v>
+        <v>0.003466002153019663</v>
       </c>
       <c r="EG18" t="n">
         <v>0</v>
@@ -10520,22 +10520,22 @@
         <v>0</v>
       </c>
       <c r="EJ18" t="n">
-        <v>-0.003408451035381646</v>
+        <v>-0.02625681375732344</v>
       </c>
       <c r="EK18" t="n">
-        <v>0.04728923408716374</v>
+        <v>0.0510532135942809</v>
       </c>
       <c r="EL18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN18" t="n">
         <v>0</v>
       </c>
       <c r="EO18" t="n">
-        <v>-0.01277627041603102</v>
+        <v>-0.03844273207820576</v>
       </c>
       <c r="EP18" t="n">
         <v>0</v>
@@ -10544,13 +10544,13 @@
         <v>-0</v>
       </c>
       <c r="ER18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES18" t="n">
-        <v>0.02803751493072065</v>
+        <v>0.006067814825159359</v>
       </c>
       <c r="ET18" t="n">
-        <v>0.002817743768328517</v>
+        <v>0.04406886628997701</v>
       </c>
       <c r="EU18" t="n">
         <v>0</v>
@@ -10562,7 +10562,7 @@
         <v>-0</v>
       </c>
       <c r="EX18" t="n">
-        <v>-0.01808398236400945</v>
+        <v>-0.05967497713790787</v>
       </c>
       <c r="EY18" t="n">
         <v>0</v>
@@ -10574,22 +10574,22 @@
         <v>0</v>
       </c>
       <c r="FB18" t="n">
-        <v>0.02408577528846209</v>
+        <v>-0.006747037493913817</v>
       </c>
       <c r="FC18" t="n">
-        <v>0.04115578127544132</v>
+        <v>0.04533085295682484</v>
       </c>
       <c r="FD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE18" t="n">
         <v>0</v>
       </c>
       <c r="FF18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG18" t="n">
-        <v>0.007376195651755181</v>
+        <v>0.127769368547643</v>
       </c>
       <c r="FH18" t="n">
         <v>-0</v>
@@ -10598,13 +10598,13 @@
         <v>0</v>
       </c>
       <c r="FJ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK18" t="n">
-        <v>0.01202097803954294</v>
+        <v>-5.861337664423544e-05</v>
       </c>
       <c r="FL18" t="n">
-        <v>-0.002121784118489793</v>
+        <v>0.1059281336776556</v>
       </c>
       <c r="FM18" t="n">
         <v>0</v>
@@ -10616,10 +10616,10 @@
         <v>-0</v>
       </c>
       <c r="FP18" t="n">
-        <v>0.0006546982649096399</v>
+        <v>0.003074093359563177</v>
       </c>
       <c r="FQ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FR18" t="n">
         <v>-0</v>
@@ -10628,13 +10628,13 @@
         <v>0</v>
       </c>
       <c r="FT18" t="n">
-        <v>-0.0006216824476783274</v>
+        <v>0.001590208613466223</v>
       </c>
       <c r="FU18" t="n">
-        <v>0.01139849522618542</v>
+        <v>0.04096364891334509</v>
       </c>
       <c r="FV18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW18" t="n">
         <v>-0</v>
@@ -10643,28 +10643,28 @@
         <v>0</v>
       </c>
       <c r="FY18" t="n">
-        <v>0.00460258118434362</v>
+        <v>0.0725763631748053</v>
       </c>
       <c r="FZ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GA18" t="n">
         <v>0</v>
       </c>
       <c r="GB18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD18" t="n">
-        <v>0.01054367872908787</v>
+        <v>0.07896609230274053</v>
       </c>
       <c r="GE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG18" t="n">
         <v>0</v>
